--- a/E/MBG01D.xlsx
+++ b/E/MBG01D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="131">
   <si>
     <t/>
   </si>
@@ -152,6 +152,15 @@
   </si>
   <si>
     <t>21</t>
+  </si>
+  <si>
+    <t>20142056</t>
+  </si>
+  <si>
+    <t>NASIKU/B BERAS PRM 5</t>
+  </si>
+  <si>
+    <t>22</t>
   </si>
   <si>
     <t>20128415</t>
@@ -787,7 +796,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F48"/>
+  <dimension ref="A1:F49"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1109,13 +1118,13 @@
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>4</v>
+        <v>49</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>49</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -1132,7 +1141,7 @@
         <v>8</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>52</v>
@@ -1152,18 +1161,18 @@
         <v>8</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>12</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
@@ -1172,7 +1181,7 @@
         <v>8</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>57</v>
+        <v>11</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>12</v>
@@ -1192,7 +1201,7 @@
         <v>8</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>12</v>
@@ -1200,10 +1209,10 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
@@ -1212,7 +1221,7 @@
         <v>8</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>62</v>
+        <v>15</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>12</v>
@@ -1229,10 +1238,10 @@
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>4</v>
+        <v>65</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>12</v>
@@ -1240,10 +1249,10 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
@@ -1252,7 +1261,7 @@
         <v>11</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>12</v>
@@ -1260,10 +1269,10 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
@@ -1272,7 +1281,7 @@
         <v>11</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>12</v>
@@ -1280,10 +1289,10 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
@@ -1292,18 +1301,18 @@
         <v>11</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>62</v>
+        <v>15</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>3</v>
@@ -1312,7 +1321,7 @@
         <v>11</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>5</v>
@@ -1352,30 +1361,30 @@
         <v>11</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>21</v>
+        <v>79</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>57</v>
+        <v>11</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>81</v>
+        <v>12</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -1389,73 +1398,73 @@
         <v>3</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>49</v>
+        <v>84</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>57</v>
+        <v>11</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>12</v>
+        <v>52</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>73</v>
+        <v>15</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>90</v>
+        <v>12</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -1469,7 +1478,7 @@
         <v>3</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>76</v>
@@ -1489,30 +1498,30 @@
         <v>3</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E35" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F35" s="1" t="s">
         <v>96</v>
-      </c>
-      <c r="F35" s="1" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B36" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="B36" s="1" t="s">
+      <c r="C36" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E36" s="1" t="s">
         <v>99</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>4</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>100</v>
@@ -1532,18 +1541,18 @@
         <v>15</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>3</v>
@@ -1552,10 +1561,10 @@
         <v>15</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -1572,7 +1581,7 @@
         <v>15</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>57</v>
+        <v>11</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>108</v>
@@ -1592,18 +1601,18 @@
         <v>15</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>3</v>
@@ -1612,18 +1621,18 @@
         <v>15</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>62</v>
+        <v>15</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>3</v>
@@ -1632,18 +1641,18 @@
         <v>15</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>3</v>
@@ -1655,15 +1664,15 @@
         <v>76</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>5</v>
+        <v>103</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>3</v>
@@ -1672,18 +1681,18 @@
         <v>15</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>100</v>
+        <v>5</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>3</v>
@@ -1692,10 +1701,10 @@
         <v>15</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>121</v>
+        <v>99</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -1712,18 +1721,18 @@
         <v>15</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>18</v>
+        <v>124</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>12</v>
+        <v>103</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>3</v>
@@ -1732,18 +1741,18 @@
         <v>15</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>3</v>
@@ -1752,9 +1761,29 @@
         <v>15</v>
       </c>
       <c r="E48" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E49" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="F48" s="1" t="s">
+      <c r="F49" s="1" t="s">
         <v>5</v>
       </c>
     </row>
